--- a/Dataset/Pengujian LoRa.xlsx
+++ b/Dataset/Pengujian LoRa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah\Semester 8\Seminar Proposal\Project\Real no Fake\Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435E5F10-0786-4E56-BDDC-9C292E2530B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F64F30E-F4BB-4018-B079-472B5A432C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{277A21D3-52C3-443A-8236-42EF92E38DDF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="19">
   <si>
     <t>RSSI</t>
   </si>
@@ -48,12 +48,6 @@
     <t>10m</t>
   </si>
   <si>
-    <t>513s</t>
-  </si>
-  <si>
-    <t>521s</t>
-  </si>
-  <si>
     <t>30m</t>
   </si>
   <si>
@@ -91,6 +85,12 @@
   </si>
   <si>
     <t>Terhalang Bangunan</t>
+  </si>
+  <si>
+    <t>Terhalang Pohon</t>
+  </si>
+  <si>
+    <t>273ms</t>
   </si>
 </sst>
 </file>
@@ -442,16 +442,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49AD79F-004C-4D12-8C5E-32BDBB7145B0}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="16.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.08984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -462,10 +463,10 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
         <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -477,13 +478,28 @@
         <v>1</v>
       </c>
       <c r="J1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -491,22 +507,31 @@
         <v>-111</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
         <v>3</v>
       </c>
+      <c r="H2">
+        <v>-112</v>
+      </c>
       <c r="J2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="M2">
+        <v>-112</v>
+      </c>
+      <c r="P2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -514,45 +539,51 @@
         <v>-112</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3" t="s">
         <v>3</v>
       </c>
       <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>-111</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>-111</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4" t="s">
         <v>3</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="P4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -560,22 +591,25 @@
         <v>-110</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
         <v>3</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="P5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -583,45 +617,51 @@
         <v>-110</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
         <v>3</v>
       </c>
       <c r="J6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>-111</v>
+      </c>
+      <c r="C7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7">
-        <v>-111</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7" t="s">
         <v>3</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="P7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -629,548 +669,620 @@
         <v>-112</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+      <c r="P8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>-111</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+      <c r="P9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>-111</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" t="s">
+        <v>16</v>
+      </c>
+      <c r="P10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>-111</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" t="s">
+        <v>16</v>
+      </c>
+      <c r="P11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12">
+        <v>-111</v>
+      </c>
+      <c r="C12" t="s">
         <v>9</v>
       </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>-111</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>-111</v>
-      </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11">
-        <v>-111</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" t="s">
-        <v>3</v>
-      </c>
-      <c r="J11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12">
-        <v>-111</v>
-      </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
       <c r="D12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="P12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B13">
         <v>-110</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="P13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B14">
         <v>-110</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="P14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B15">
         <v>-110</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" t="s">
+        <v>16</v>
+      </c>
+      <c r="P15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>-111</v>
+      </c>
+      <c r="C16" t="s">
         <v>9</v>
       </c>
-      <c r="E15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" t="s">
-        <v>7</v>
-      </c>
-      <c r="J15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16">
-        <v>-111</v>
-      </c>
-      <c r="C16" t="s">
-        <v>11</v>
-      </c>
       <c r="D16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" t="s">
+        <v>16</v>
+      </c>
+      <c r="P16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>-111</v>
+      </c>
+      <c r="C17" t="s">
         <v>9</v>
       </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" t="s">
-        <v>7</v>
-      </c>
-      <c r="J16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17">
-        <v>-111</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
       <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" t="s">
+        <v>16</v>
+      </c>
+      <c r="P17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18">
+        <v>-111</v>
+      </c>
+      <c r="C18" t="s">
         <v>9</v>
       </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" t="s">
-        <v>7</v>
-      </c>
-      <c r="J17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18">
-        <v>-111</v>
-      </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
       <c r="D18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" t="s">
+        <v>16</v>
+      </c>
+      <c r="P18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19">
+        <v>-111</v>
+      </c>
+      <c r="C19" t="s">
         <v>9</v>
       </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" t="s">
-        <v>7</v>
-      </c>
-      <c r="J18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19">
-        <v>-111</v>
-      </c>
-      <c r="C19" t="s">
-        <v>11</v>
-      </c>
       <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" t="s">
+        <v>5</v>
+      </c>
+      <c r="J19" t="s">
+        <v>16</v>
+      </c>
+      <c r="P19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>-111</v>
+      </c>
+      <c r="C20" t="s">
         <v>9</v>
       </c>
-      <c r="E19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" t="s">
-        <v>7</v>
-      </c>
-      <c r="J19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20">
-        <v>-111</v>
-      </c>
-      <c r="C20" t="s">
-        <v>11</v>
-      </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G20" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="P20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B21">
         <v>-112</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="P21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B22">
         <v>-112</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J22" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="P22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B23">
         <v>-110</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E23" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="P23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B24">
         <v>-112</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="P24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B25">
         <v>-109</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s">
+        <v>4</v>
+      </c>
+      <c r="J25" t="s">
+        <v>16</v>
+      </c>
+      <c r="P25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>-111</v>
+      </c>
+      <c r="C26" t="s">
         <v>12</v>
       </c>
-      <c r="G25" t="s">
-        <v>6</v>
-      </c>
-      <c r="J25" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26">
-        <v>-111</v>
-      </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="P26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B27">
         <v>-112</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="P27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B28">
         <v>-111</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G28" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="P28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B29">
         <v>-112</v>
       </c>
       <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" t="s">
+        <v>4</v>
+      </c>
+      <c r="J29" t="s">
+        <v>16</v>
+      </c>
+      <c r="P29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>-111</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" t="s">
+        <v>4</v>
+      </c>
+      <c r="J30" t="s">
+        <v>16</v>
+      </c>
+      <c r="P30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>-111</v>
+      </c>
+      <c r="C31" t="s">
         <v>15</v>
       </c>
-      <c r="D29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" t="s">
-        <v>6</v>
-      </c>
-      <c r="J29" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30">
-        <v>-111</v>
-      </c>
-      <c r="C30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" t="s">
-        <v>6</v>
-      </c>
-      <c r="J30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31">
-        <v>-111</v>
-      </c>
-      <c r="C31" t="s">
-        <v>17</v>
-      </c>
       <c r="D31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G31" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="P31" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
